--- a/samples/cafe-full.xlsx
+++ b/samples/cafe-full.xlsx
@@ -1512,7 +1512,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" error="Enter 1, 2 or 3" errorStyle="stop" errorTitle="Scenario" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B4" type="list">
+    <dataValidation allowBlank="false" error="Enter 1, 2 or 3" errorStyle="stop" errorTitle="Scenario" operator="between" prompt="1 = Low, 2 = Base, 3 = High. Every sheet recalculates." promptTitle="Scenario" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B4" type="list">
       <formula1>"1,2,3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
